--- a/Entrega 02/Bravo_Visitas_Wikipedia_database/Base de datos Wikipedia.xlsx
+++ b/Entrega 02/Bravo_Visitas_Wikipedia_database/Base de datos Wikipedia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/virginia_bravo_uc_cl/Documents/Universidad/7° semestre/Narración gráfica/Proyecto-Arratia-Bravo-Finkenberger/Entrega 02/Bravo_Visitas_Wikipedia_database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E5375A3-1A69-4806-9DF8-B2D5B37DBAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{6E5375A3-1A69-4806-9DF8-B2D5B37DBAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD81BE94-EA13-4E6D-9712-332598457D08}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="407">
   <si>
     <t>ID</t>
   </si>
@@ -502,6 +502,760 @@
   </si>
   <si>
     <t>https://trends.google.es/trends/explore?date=2025-09-25%202026-03-25&amp;q=Aegla%20denticulata&amp;hl=es</t>
+  </si>
+  <si>
+    <t>Acalodegma vidali</t>
+  </si>
+  <si>
+    <t>Aegla bahamondei</t>
+  </si>
+  <si>
+    <t>Pancora</t>
+  </si>
+  <si>
+    <t>Aegla concepcionensis</t>
+  </si>
+  <si>
+    <t>Aegla expansa</t>
+  </si>
+  <si>
+    <t>Aegla laevis</t>
+  </si>
+  <si>
+    <t>Aegla occidentalis</t>
+  </si>
+  <si>
+    <t>Aegla papudo</t>
+  </si>
+  <si>
+    <t>Allograpta robinsoniana</t>
+  </si>
+  <si>
+    <t>Mosca florícola de Juan Fernández</t>
+  </si>
+  <si>
+    <t>Alsodes barrioi</t>
+  </si>
+  <si>
+    <t>Sapo de Barros</t>
+  </si>
+  <si>
+    <t>Alsodes cantillanensis</t>
+  </si>
+  <si>
+    <t>Sapo</t>
+  </si>
+  <si>
+    <t>Alsodes montanus</t>
+  </si>
+  <si>
+    <t>Sapo de monte</t>
+  </si>
+  <si>
+    <t>Alsodes tumultuosus</t>
+  </si>
+  <si>
+    <t>Alsodes valdiviensis</t>
+  </si>
+  <si>
+    <t>Rana de pecho espinoso de Cordillera Pelada</t>
+  </si>
+  <si>
+    <t>Alsodes vanzolinii</t>
+  </si>
+  <si>
+    <t>Sapo de Vanzolini</t>
+  </si>
+  <si>
+    <t>Alsodes verrucosus</t>
+  </si>
+  <si>
+    <t>Sapo de pecho espinoso de verrugas</t>
+  </si>
+  <si>
+    <t>Alyma quiriquinaensis</t>
+  </si>
+  <si>
+    <t>Típula pintada</t>
+  </si>
+  <si>
+    <t>Americobdella valdiviana</t>
+  </si>
+  <si>
+    <t>Liguay, sanguijuela gigante valdiviana</t>
+  </si>
+  <si>
+    <t>Amphidoxa arctispira</t>
+  </si>
+  <si>
+    <t>Caracol terrestre Amphidoxa</t>
+  </si>
+  <si>
+    <t>Amphidoxa ceroides</t>
+  </si>
+  <si>
+    <t>Amphidoxa helicophantoides</t>
+  </si>
+  <si>
+    <t>Amphidoxa marmorella</t>
+  </si>
+  <si>
+    <t>Amphidoxa pusio</t>
+  </si>
+  <si>
+    <t>Amphidoxa quadrata</t>
+  </si>
+  <si>
+    <t>Amphidoxa selkirki</t>
+  </si>
+  <si>
+    <t>Amphidoxa tessellata</t>
+  </si>
+  <si>
+    <t>Anairetes fernandezianus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cachudito de Juan Fernández </t>
+  </si>
+  <si>
+    <t>Aplochiton marinus</t>
+  </si>
+  <si>
+    <t>Peladilla</t>
+  </si>
+  <si>
+    <t>Aplochiton zebra</t>
+  </si>
+  <si>
+    <t>Apterodorcus tristis</t>
+  </si>
+  <si>
+    <t>Mancapollo, pica pollo, borracho, borrachito, buey</t>
+  </si>
+  <si>
+    <t>Ardenna creatopus</t>
+  </si>
+  <si>
+    <t>Fardela blanca</t>
+  </si>
+  <si>
+    <t>Bolborhinum trilobulicorne</t>
+  </si>
+  <si>
+    <t>Escarabajo</t>
+  </si>
+  <si>
+    <t>Brachistosternus cepedai</t>
+  </si>
+  <si>
+    <t>Escorpión de Cepeda</t>
+  </si>
+  <si>
+    <t>Bullockia maldonadoi</t>
+  </si>
+  <si>
+    <t>Bagrecito</t>
+  </si>
+  <si>
+    <t>Callyntra cantillana</t>
+  </si>
+  <si>
+    <t>Cascarudo de Cantillana</t>
+  </si>
+  <si>
+    <t>Callyntra multicosta</t>
+  </si>
+  <si>
+    <t>Cascarudo de Las Docas</t>
+  </si>
+  <si>
+    <t>Callyntra penai</t>
+  </si>
+  <si>
+    <t>Cascarudo de Peña</t>
+  </si>
+  <si>
+    <t>Callyntra planiuscula</t>
+  </si>
+  <si>
+    <t>Cascarudo de la Plata</t>
+  </si>
+  <si>
+    <t>Charopa involuta</t>
+  </si>
+  <si>
+    <t>Caracol terrestre Charopa</t>
+  </si>
+  <si>
+    <t>Charopa masafuerae</t>
+  </si>
+  <si>
+    <t>Cheirodon kiliani</t>
+  </si>
+  <si>
+    <t>Pocha</t>
+  </si>
+  <si>
+    <t>Chileputo chilensis</t>
+  </si>
+  <si>
+    <t>Chanchito blanco de la araucaria</t>
+  </si>
+  <si>
+    <t>Chinchilla lanigera</t>
+  </si>
+  <si>
+    <t>Chinchilla costina</t>
+  </si>
+  <si>
+    <t>Chrysiptera rapanui</t>
+  </si>
+  <si>
+    <t>Mamata</t>
+  </si>
+  <si>
+    <t>Cnemalobus hirsutus</t>
+  </si>
+  <si>
+    <t>Cnemalobus nuria</t>
+  </si>
+  <si>
+    <t>Conognatha azarae fisheri</t>
+  </si>
+  <si>
+    <t>Balita, insecto joya de Fisher</t>
+  </si>
+  <si>
+    <t>Conognatha leechi</t>
+  </si>
+  <si>
+    <t>Balita, insecto joya de Leech</t>
+  </si>
+  <si>
+    <t>Diplomystes camposensis</t>
+  </si>
+  <si>
+    <t>Tollo</t>
+  </si>
+  <si>
+    <t>Diplomystes chilensis</t>
+  </si>
+  <si>
+    <t>Tollo de agua dulce</t>
+  </si>
+  <si>
+    <t>Diplomystes nahuelbutaensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tollo </t>
+  </si>
+  <si>
+    <t>Enodisomacris curtipennis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langosta de alas cortas; langosta de Ureta; langosta de Lila; langosta de La Chimba
+</t>
+  </si>
+  <si>
+    <t>Erichius virgatus</t>
+  </si>
+  <si>
+    <t>Borrachito de Tolhuaca, borrachito listado de Tolhuaca</t>
+  </si>
+  <si>
+    <t>Euathlus affinis</t>
+  </si>
+  <si>
+    <t>Tarántula afín de Santiago</t>
+  </si>
+  <si>
+    <t>Eupsophus altor</t>
+  </si>
+  <si>
+    <t>Rana de hojarasca de Oncol</t>
+  </si>
+  <si>
+    <t>Eupsophus contulmoensis</t>
+  </si>
+  <si>
+    <t>Sapo de Contulmo</t>
+  </si>
+  <si>
+    <t>Eupsophus insularis</t>
+  </si>
+  <si>
+    <t>Sapo de Isla Mocha</t>
+  </si>
+  <si>
+    <t>Eupsophus migueli</t>
+  </si>
+  <si>
+    <t>Sapo de Miguel</t>
+  </si>
+  <si>
+    <t>Eupsophus nahuelbutensis</t>
+  </si>
+  <si>
+    <t>Sapo de Nahuelbuta</t>
+  </si>
+  <si>
+    <t>Eupsophus septentrionalis</t>
+  </si>
+  <si>
+    <t>Ranita de Los Queules</t>
+  </si>
+  <si>
+    <t>Exallococcus laureliae</t>
+  </si>
+  <si>
+    <t>Cochinilla de fieltro (genérico)</t>
+  </si>
+  <si>
+    <t>Falco sparverius fernandenzis</t>
+  </si>
+  <si>
+    <t>Cernícalo de Juan Fernández</t>
+  </si>
+  <si>
+    <t>Fernandezia bulimoides</t>
+  </si>
+  <si>
+    <t>Caracol terrestre de Juan Fernández</t>
+  </si>
+  <si>
+    <t>Fernandezia conifera</t>
+  </si>
+  <si>
+    <t>Fernandezia consimilis</t>
+  </si>
+  <si>
+    <t>Fernandezia cylindrella</t>
+  </si>
+  <si>
+    <t>Fernandezia diaphana</t>
+  </si>
+  <si>
+    <t>Fernandezia expansa</t>
+  </si>
+  <si>
+    <t>Fernandezia inornata</t>
+  </si>
+  <si>
+    <t>Fernandezia longa</t>
+  </si>
+  <si>
+    <t>Fernandezia philippiana</t>
+  </si>
+  <si>
+    <t>Fernandezia splendida</t>
+  </si>
+  <si>
+    <t>Fernandezia tryoni</t>
+  </si>
+  <si>
+    <t>Fernandezia wilsoni</t>
+  </si>
+  <si>
+    <t>Galaxias globiceps</t>
+  </si>
+  <si>
+    <t>Puye</t>
+  </si>
+  <si>
+    <t>Gyriosomus angustus</t>
+  </si>
+  <si>
+    <t>Vaquita del desierto de Paposo</t>
+  </si>
+  <si>
+    <t>Heleobia ascotanensis</t>
+  </si>
+  <si>
+    <t>Caracol</t>
+  </si>
+  <si>
+    <t>Henicotherus francisca</t>
+  </si>
+  <si>
+    <t>No conocido</t>
+  </si>
+  <si>
+    <t>Homoeomma orellanai</t>
+  </si>
+  <si>
+    <t>Tarántula enana de penacho amarillo, araña pollito</t>
+  </si>
+  <si>
+    <t>Insuetophrynus acarpicus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sapo </t>
+  </si>
+  <si>
+    <t>Lasia pulla</t>
+  </si>
+  <si>
+    <t>Mosca colibrí enana</t>
+  </si>
+  <si>
+    <t>Liolaemus buergeri</t>
+  </si>
+  <si>
+    <t>Lagartija de Bürger</t>
+  </si>
+  <si>
+    <t>Liolaemus carlosgarini</t>
+  </si>
+  <si>
+    <t>Lagartija de Garín</t>
+  </si>
+  <si>
+    <t>Liolaemus chillanensis</t>
+  </si>
+  <si>
+    <t>Lagarto de Chillán</t>
+  </si>
+  <si>
+    <t>Liolaemus fabiani</t>
+  </si>
+  <si>
+    <t>Lagartija de Fabián</t>
+  </si>
+  <si>
+    <t>Liolaemus foxi</t>
+  </si>
+  <si>
+    <t>Lagartija de Fox</t>
+  </si>
+  <si>
+    <t>Liolaemus frassinettii</t>
+  </si>
+  <si>
+    <t>Lagartija del Cerro Cantillana, lagarto de Frassinetti</t>
+  </si>
+  <si>
+    <t>Liolaemus leftrarui</t>
+  </si>
+  <si>
+    <t>Lagartija de Leftraru, Leftraru’s Lizard (Inglés)</t>
+  </si>
+  <si>
+    <t>Liolaemus leopardinus</t>
+  </si>
+  <si>
+    <t>Lagarto leopardo</t>
+  </si>
+  <si>
+    <t>Liolaemus manueli</t>
+  </si>
+  <si>
+    <t>Lagartija de Manuel</t>
+  </si>
+  <si>
+    <t>Liolaemus nigrocoeruleus</t>
+  </si>
+  <si>
+    <t>Lagartija negro azulada, Black Bluish Lizard (Inglés)</t>
+  </si>
+  <si>
+    <t>Liolaemus poconchilensis</t>
+  </si>
+  <si>
+    <t>Lagarto de Poconchile</t>
+  </si>
+  <si>
+    <t>Liolaemus scorialis</t>
+  </si>
+  <si>
+    <t>Lagarto del escorial, Slag Lizard (Inglés)</t>
+  </si>
+  <si>
+    <t>Liolaemus septentrionalis</t>
+  </si>
+  <si>
+    <t>Lagartija pintada septentrional, Northern Painted Lizard (Inglés)</t>
+  </si>
+  <si>
+    <t>Liolaemus ubaghsi</t>
+  </si>
+  <si>
+    <t>Lagarto leopardo de Ubaghs, Ubaghs’ Leopard Lizard (Inglés)</t>
+  </si>
+  <si>
+    <t>Liolaemus villaricensis</t>
+  </si>
+  <si>
+    <t>Lagartija</t>
+  </si>
+  <si>
+    <t>Luispenaia paposo</t>
+  </si>
+  <si>
+    <t>Pololo de Paposo</t>
+  </si>
+  <si>
+    <t>Lycalopex fulvipes</t>
+  </si>
+  <si>
+    <t>Zorro de Chiloé</t>
+  </si>
+  <si>
+    <t>Lynceus huentelauquensis</t>
+  </si>
+  <si>
+    <t>Camarón almeja de Huentelauquén</t>
+  </si>
+  <si>
+    <t>Mordacia lapicida</t>
+  </si>
+  <si>
+    <t>Lamprea de agua dulce</t>
+  </si>
+  <si>
+    <t>Nematogenys inermis</t>
+  </si>
+  <si>
+    <t>Bagre grande</t>
+  </si>
+  <si>
+    <t>Neuquenaphis staryi</t>
+  </si>
+  <si>
+    <t>No tiene, se propone "pulgón del Ruíl"</t>
+  </si>
+  <si>
+    <t>Nycterinus angusticollis</t>
+  </si>
+  <si>
+    <t>Insecto joya</t>
+  </si>
+  <si>
+    <t>Nycterinus borealis</t>
+  </si>
+  <si>
+    <t>Cucaracho negro</t>
+  </si>
+  <si>
+    <t>Nycterinus mannerheimi</t>
+  </si>
+  <si>
+    <t>Tenebrio de Mannerheim, teatino de Mannerheim</t>
+  </si>
+  <si>
+    <t>Oogenius castilloi</t>
+  </si>
+  <si>
+    <t>Oogenius penai</t>
+  </si>
+  <si>
+    <t>Orestias ascotanensis</t>
+  </si>
+  <si>
+    <t>Karachi, orestias</t>
+  </si>
+  <si>
+    <t>Orestias chungarensis</t>
+  </si>
+  <si>
+    <t>Orestias laucaensis</t>
+  </si>
+  <si>
+    <t>Orestias parinacotensis</t>
+  </si>
+  <si>
+    <t>Paropisthopatus umbrinus</t>
+  </si>
+  <si>
+    <t>Gusano aterciopelado, onicóforo (genérico)</t>
+  </si>
+  <si>
+    <t>Percilia gillissi</t>
+  </si>
+  <si>
+    <t>Carmelita</t>
+  </si>
+  <si>
+    <t>Percilia irwini</t>
+  </si>
+  <si>
+    <t>Carmelita de Concepción</t>
+  </si>
+  <si>
+    <t>Phyllopetalia altarensis</t>
+  </si>
+  <si>
+    <t>Phymaturus bibronii</t>
+  </si>
+  <si>
+    <t>Matuasto de Bibron</t>
+  </si>
+  <si>
+    <t>Phymaturus darwini</t>
+  </si>
+  <si>
+    <t>Matuasto de Darwin, lagarto de cola gruesa</t>
+  </si>
+  <si>
+    <t>Phymaturus maulense</t>
+  </si>
+  <si>
+    <t>Matuasto</t>
+  </si>
+  <si>
+    <t>Plectostylus araucanus</t>
+  </si>
+  <si>
+    <t>Caracol de árbol araucano, caracol de árbol</t>
+  </si>
+  <si>
+    <t>Praocis aenea</t>
+  </si>
+  <si>
+    <t>Vaquita</t>
+  </si>
+  <si>
+    <t>Praocis bicentenario</t>
+  </si>
+  <si>
+    <t>Vaquita del bicentenario</t>
+  </si>
+  <si>
+    <t>Pristidactylus valeriae</t>
+  </si>
+  <si>
+    <t>Gruñidor de Valeria</t>
+  </si>
+  <si>
+    <t>Pristidactylus volcanensis</t>
+  </si>
+  <si>
+    <t>Gruñidor de El Volcán</t>
+  </si>
+  <si>
+    <t>Pterodroma externa</t>
+  </si>
+  <si>
+    <t>Fardela blanca de Juan Fernández, petrel de Juan Fernández</t>
+  </si>
+  <si>
+    <t>Pterodroma longirostris</t>
+  </si>
+  <si>
+    <t>Fardela de Más Afuera</t>
+  </si>
+  <si>
+    <t>Ptychodon oculta</t>
+  </si>
+  <si>
+    <t>Caracol terrestre Ptychodon</t>
+  </si>
+  <si>
+    <t>Ptychodon skottsberg</t>
+  </si>
+  <si>
+    <t>Scotobius planicosta</t>
+  </si>
+  <si>
+    <t>Succinea fragilis</t>
+  </si>
+  <si>
+    <t>Caracol terrestre Succinea</t>
+  </si>
+  <si>
+    <t>Succinea mamillata</t>
+  </si>
+  <si>
+    <t>Succinea pinguis</t>
+  </si>
+  <si>
+    <t>Telmatobius pefauri</t>
+  </si>
+  <si>
+    <t>Sapo de Pefaur</t>
+  </si>
+  <si>
+    <t>Telmatobius philippii</t>
+  </si>
+  <si>
+    <t>Sapo de Philippi</t>
+  </si>
+  <si>
+    <t>Telmatobius zapahuirensis</t>
+  </si>
+  <si>
+    <t>Sapo de Zapahuira</t>
+  </si>
+  <si>
+    <t>Telmatobufo ignotus</t>
+  </si>
+  <si>
+    <t>Rana montana de Los Queules</t>
+  </si>
+  <si>
+    <t>Telmatobufo venustus</t>
+  </si>
+  <si>
+    <t>Sapo hermoso</t>
+  </si>
+  <si>
+    <t>Tornatellina minuta</t>
+  </si>
+  <si>
+    <t>Caracol terrestre Tornatellina</t>
+  </si>
+  <si>
+    <t>Trichomycterus chiltoni</t>
+  </si>
+  <si>
+    <t>Trichomycterus chungaraensis</t>
+  </si>
+  <si>
+    <t>Trichomycterus laucaensis</t>
+  </si>
+  <si>
+    <t>Trichomycterus rivulatus</t>
+  </si>
+  <si>
+    <t>Uretacris lilai</t>
+  </si>
+  <si>
+    <t>Langosta de Ureta, langosta de Lila, langosta de La Chimba</t>
+  </si>
+  <si>
+    <t>Valdiviomyia gigantea</t>
+  </si>
+  <si>
+    <t>Mosca florícola valdiviana gigante</t>
+  </si>
+  <si>
+    <t>Virilastacus rucapihuelensis</t>
+  </si>
+  <si>
+    <t>Camarón</t>
+  </si>
+  <si>
+    <t>RCE</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>Clitellata</t>
+  </si>
+  <si>
+    <t>Mammalia</t>
+  </si>
+  <si>
+    <t>Branchiopoda</t>
+  </si>
+  <si>
+    <t>Cephalaspidomorphi</t>
+  </si>
+  <si>
+    <t>Udeonycophora</t>
   </si>
 </sst>
 </file>
@@ -600,7 +1354,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -655,13 +1409,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{89BB7450-1A81-45B0-B874-B6809C9189F6}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -808,6 +1602,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCC99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -819,18 +1618,15 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B98F516A-28D6-4FB9-81F1-2C9D94D3A83A}" name="Tabla1" displayName="Tabla1" ref="A1:G71" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:G71" xr:uid="{B98F516A-28D6-4FB9-81F1-2C9D94D3A83A}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B98F516A-28D6-4FB9-81F1-2C9D94D3A83A}" name="Tabla1" displayName="Tabla1" ref="A1:H214" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:H214" xr:uid="{B98F516A-28D6-4FB9-81F1-2C9D94D3A83A}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{69238F2A-162D-43B2-B7D8-3FC81F366EB5}" name="ID"/>
     <tableColumn id="2" xr3:uid="{C4600FDA-7C40-4DD2-9789-0BB1AAB9FD6C}" name="Nombre Científico"/>
-    <tableColumn id="3" xr3:uid="{CE4C8329-49D0-4CC8-9B40-2F4DF03567EA}" name="Nombre Común" dataDxfId="1" dataCellStyle="Normal 3"/>
-    <tableColumn id="4" xr3:uid="{F3492727-C5D3-47DB-AF46-5C37ACDF0D69}" name="Clase" dataDxfId="0" dataCellStyle="Normal 3"/>
+    <tableColumn id="3" xr3:uid="{CE4C8329-49D0-4CC8-9B40-2F4DF03567EA}" name="Nombre Común" dataDxfId="2" dataCellStyle="Normal 3"/>
+    <tableColumn id="4" xr3:uid="{F3492727-C5D3-47DB-AF46-5C37ACDF0D69}" name="Clase" dataDxfId="1" dataCellStyle="Normal 3"/>
+    <tableColumn id="8" xr3:uid="{921C02FC-09F8-4E9F-B1D3-DB11520FB7B4}" name="RCE" dataDxfId="0" dataCellStyle="Normal 3"/>
     <tableColumn id="5" xr3:uid="{12740CEA-0AA5-4754-B7DD-623297E7B35A}" name="Total Visitas (periodo seis meses)"/>
     <tableColumn id="6" xr3:uid="{B4BA12EB-B3A2-402E-B1FA-B15181DC5518}" name="Promedio Diario"/>
     <tableColumn id="7" xr3:uid="{AEDF878D-AD24-4893-80F2-71AEBCDD79B7}" name="URL Fuente"/>
@@ -840,15 +1636,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC424899-A335-4FA2-8F84-9F94794E961E}" name="Tabla13" displayName="Tabla13" ref="A1:G71" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC424899-A335-4FA2-8F84-9F94794E961E}" name="Tabla13" displayName="Tabla13" ref="A1:G71" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A1:G71" xr:uid="{CC424899-A335-4FA2-8F84-9F94794E961E}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{7B6ADD57-2AF2-4072-B5D8-1880205CE9A5}" name="ID"/>
     <tableColumn id="2" xr3:uid="{D16FBD1F-8DF8-4BDE-862D-01F3F795FA54}" name="Nombre Científico"/>
     <tableColumn id="3" xr3:uid="{56C7319F-7697-4487-A8D3-44167E195F63}" name="Nombre Común"/>
-    <tableColumn id="4" xr3:uid="{4C399304-441A-4F20-9CEC-365CE3512923}" name="Clase" dataDxfId="4" dataCellStyle="Normal 3"/>
+    <tableColumn id="4" xr3:uid="{4C399304-441A-4F20-9CEC-365CE3512923}" name="Clase" dataDxfId="5" dataCellStyle="Normal 3"/>
     <tableColumn id="5" xr3:uid="{21FEE130-6481-43AD-B17B-B8C5E9F82053}" name="Total Visitas (periodo seis meses)"/>
-    <tableColumn id="6" xr3:uid="{88E9B6A2-CB3B-437F-900D-AD2A3C66477A}" name="Promedio Diario" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{88E9B6A2-CB3B-437F-900D-AD2A3C66477A}" name="Promedio Diario" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{67241A42-4BE2-4BBC-84BC-0F4CE1700BF5}" name="URL Fuente"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1056,17 +1852,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:H214"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="31.90625" customWidth="1"/>
-    <col min="3" max="4" width="20.6328125" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="20.26953125" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="3" max="5" width="20.6328125" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" customWidth="1"/>
+    <col min="8" max="8" width="144.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1080,16 +1876,19 @@
         <v>124</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1102,17 +1901,20 @@
       <c r="D2" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F2" s="1">
         <v>97</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1125,15 +1927,18 @@
       <c r="D3" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>141</v>
+      <c r="E3" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1146,15 +1951,18 @@
       <c r="D4" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>141</v>
+      <c r="E4" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1167,17 +1975,20 @@
       <c r="D5" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F5">
         <v>32</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="H5" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1190,17 +2001,20 @@
       <c r="D6" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F6">
         <v>168</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="H6" s="16" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1213,17 +2027,20 @@
       <c r="D7" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F7">
         <v>643</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="H7" s="16" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1236,14 +2053,17 @@
       <c r="D8" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="E8" t="s">
-        <v>136</v>
+      <c r="E8" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F8" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1256,14 +2076,17 @@
       <c r="D9" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E9" t="s">
-        <v>136</v>
+      <c r="E9" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F9" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1276,17 +2099,20 @@
       <c r="D10" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F10">
         <v>113</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="H10" s="17" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1299,14 +2125,17 @@
       <c r="D11" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E11" t="s">
-        <v>141</v>
+      <c r="E11" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F11" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1319,14 +2148,17 @@
       <c r="D12" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E12" t="s">
-        <v>141</v>
+      <c r="E12" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F12" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1339,14 +2171,17 @@
       <c r="D13" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E13" t="s">
-        <v>141</v>
+      <c r="E13" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1359,14 +2194,17 @@
       <c r="D14" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E14" t="s">
-        <v>141</v>
+      <c r="E14" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F14" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1379,14 +2217,17 @@
       <c r="D15" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E15" t="s">
-        <v>136</v>
+      <c r="E15" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F15" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1399,14 +2240,17 @@
       <c r="D16" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="E16" t="s">
-        <v>141</v>
+      <c r="E16" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F16" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G16" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1419,14 +2263,17 @@
       <c r="D17" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E17" t="s">
-        <v>136</v>
+      <c r="E17" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F17" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1439,14 +2286,17 @@
       <c r="D18" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="E18" t="s">
-        <v>141</v>
+      <c r="E18" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F18" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1457,14 +2307,17 @@
       <c r="D19" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E19" t="s">
-        <v>141</v>
+      <c r="E19" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F19" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1477,14 +2330,17 @@
       <c r="D20" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E20" t="s">
-        <v>141</v>
+      <c r="E20" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F20" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G20" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1497,14 +2353,17 @@
       <c r="D21" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E21" t="s">
-        <v>141</v>
+      <c r="E21" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F21" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1517,14 +2376,17 @@
       <c r="D22" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E22" t="s">
-        <v>141</v>
+      <c r="E22" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F22" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1537,14 +2399,17 @@
       <c r="D23" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E23" t="s">
-        <v>141</v>
+      <c r="E23" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F23" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1557,14 +2422,17 @@
       <c r="D24" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E24" t="s">
-        <v>141</v>
+      <c r="E24" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F24" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1577,14 +2445,17 @@
       <c r="D25" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E25" t="s">
-        <v>141</v>
+      <c r="E25" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F25" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1597,17 +2468,20 @@
       <c r="D26" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F26">
         <v>215</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>1</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="H26" s="17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1">
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1620,14 +2494,17 @@
       <c r="D27" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E27" t="s">
-        <v>141</v>
+      <c r="E27" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F27" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G27" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1640,14 +2517,17 @@
       <c r="D28" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E28" t="s">
-        <v>141</v>
+      <c r="E28" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F28" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1660,14 +2540,17 @@
       <c r="D29" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E29" t="s">
-        <v>141</v>
+      <c r="E29" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F29" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G29" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1680,14 +2563,17 @@
       <c r="D30" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E30" t="s">
-        <v>141</v>
+      <c r="E30" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F30" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G30" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1700,14 +2586,17 @@
       <c r="D31" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E31" t="s">
-        <v>141</v>
+      <c r="E31" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F31" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1720,14 +2609,17 @@
       <c r="D32" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E32" t="s">
-        <v>141</v>
+      <c r="E32" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F32" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1740,14 +2632,17 @@
       <c r="D33" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E33" t="s">
-        <v>141</v>
+      <c r="E33" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F33" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G33" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1760,14 +2655,17 @@
       <c r="D34" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="E34" t="s">
-        <v>141</v>
+      <c r="E34" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F34" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1778,14 +2676,17 @@
       <c r="D35" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E35" t="s">
-        <v>141</v>
+      <c r="E35" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F35" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G35" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1798,14 +2699,17 @@
       <c r="D36" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E36" t="s">
-        <v>141</v>
+      <c r="E36" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F36" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G36" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1818,14 +2722,17 @@
       <c r="D37" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E37" t="s">
-        <v>141</v>
+      <c r="E37" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F37" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1838,14 +2745,17 @@
       <c r="D38" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E38" t="s">
-        <v>141</v>
+      <c r="E38" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F38" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1858,14 +2768,17 @@
       <c r="D39" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="E39" t="s">
-        <v>136</v>
+      <c r="E39" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F39" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1878,14 +2791,17 @@
       <c r="D40" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E40" t="s">
-        <v>141</v>
+      <c r="E40" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F40" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1896,14 +2812,17 @@
       <c r="D41" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E41" t="s">
-        <v>141</v>
+      <c r="E41" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F41" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1916,14 +2835,17 @@
       <c r="D42" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E42" t="s">
-        <v>141</v>
+      <c r="E42" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F42" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G42" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1936,17 +2858,20 @@
       <c r="D43" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F43">
         <v>178</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>1</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="H43" s="17" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1">
+    <row r="44" spans="1:8" ht="15.75" customHeight="1">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1959,14 +2884,17 @@
       <c r="D44" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="E44" t="s">
-        <v>141</v>
+      <c r="E44" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F44" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1977,14 +2905,17 @@
       <c r="D45" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E45" t="s">
-        <v>141</v>
+      <c r="E45" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F45" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1997,17 +2928,20 @@
       <c r="D46" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F46">
         <v>157</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>1</v>
       </c>
-      <c r="G46" s="17" t="s">
+      <c r="H46" s="17" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1">
+    <row r="47" spans="1:8" ht="15.75" customHeight="1">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -2020,17 +2954,20 @@
       <c r="D47" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F47">
         <v>5</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>0</v>
       </c>
-      <c r="G47" s="17" t="s">
+      <c r="H47" s="17" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1">
+    <row r="48" spans="1:8" ht="15.75" customHeight="1">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -2043,14 +2980,17 @@
       <c r="D48" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E48" t="s">
-        <v>141</v>
+      <c r="E48" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F48" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" customHeight="1">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -2063,14 +3003,17 @@
       <c r="D49" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E49" t="s">
-        <v>141</v>
+      <c r="E49" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F49" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G49" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" customHeight="1">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -2083,17 +3026,20 @@
       <c r="D50" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F50">
         <v>297</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>2</v>
       </c>
-      <c r="G50" s="17" t="s">
+      <c r="H50" s="17" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15.75" customHeight="1">
+    <row r="51" spans="1:8" ht="15.75" customHeight="1">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -2106,14 +3052,17 @@
       <c r="D51" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E51" t="s">
-        <v>136</v>
+      <c r="E51" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F51" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G51" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" customHeight="1">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -2126,17 +3075,20 @@
       <c r="D52" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F52">
         <v>317</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>2</v>
       </c>
-      <c r="G52" s="17" t="s">
+      <c r="H52" s="17" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.75" customHeight="1">
+    <row r="53" spans="1:8" ht="15.75" customHeight="1">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -2149,17 +3101,20 @@
       <c r="D53" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F53">
         <v>87</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>0</v>
       </c>
-      <c r="G53" s="17" t="s">
+      <c r="H53" s="17" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15.75" customHeight="1">
+    <row r="54" spans="1:8" ht="15.75" customHeight="1">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -2172,14 +3127,17 @@
       <c r="D54" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E54" t="s">
-        <v>141</v>
+      <c r="E54" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F54" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G54" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" customHeight="1">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2192,14 +3150,17 @@
       <c r="D55" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E55" t="s">
-        <v>141</v>
+      <c r="E55" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F55" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G55" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" customHeight="1">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2212,14 +3173,17 @@
       <c r="D56" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E56" t="s">
-        <v>141</v>
+      <c r="E56" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F56" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G56" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" customHeight="1">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -2232,14 +3196,17 @@
       <c r="D57" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E57" t="s">
-        <v>141</v>
+      <c r="E57" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F57" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G57" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -2252,14 +3219,17 @@
       <c r="D58" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E58" t="s">
-        <v>141</v>
+      <c r="E58" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F58" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G58" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -2272,14 +3242,17 @@
       <c r="D59" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E59" t="s">
-        <v>141</v>
+      <c r="E59" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F59" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G59" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" customHeight="1">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -2292,14 +3265,17 @@
       <c r="D60" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E60" t="s">
-        <v>141</v>
+      <c r="E60" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F60" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G60" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" customHeight="1">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -2312,14 +3288,17 @@
       <c r="D61" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="E61" t="s">
-        <v>141</v>
+      <c r="E61" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F61" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G61" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" customHeight="1">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2332,17 +3311,20 @@
       <c r="D62" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F62">
         <v>171</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>1</v>
       </c>
-      <c r="G62" s="16" t="s">
+      <c r="H62" s="16" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1">
+    <row r="63" spans="1:8" ht="15.75" customHeight="1">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -2355,17 +3337,20 @@
       <c r="D63" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F63">
         <v>686</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>4</v>
       </c>
-      <c r="G63" s="16" t="s">
+      <c r="H63" s="16" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1">
+    <row r="64" spans="1:8" ht="15.75" customHeight="1">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -2378,17 +3363,20 @@
       <c r="D64" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F64">
         <v>118</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>1</v>
       </c>
-      <c r="G64" s="16" t="s">
+      <c r="H64" s="16" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1">
+    <row r="65" spans="1:8" ht="15.75" customHeight="1">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2401,17 +3389,20 @@
       <c r="D65" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F65">
         <v>418</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>2</v>
       </c>
-      <c r="G65" s="17" t="s">
+      <c r="H65" s="17" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1">
+    <row r="66" spans="1:8" ht="15.75" customHeight="1">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -2424,17 +3415,20 @@
       <c r="D66" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="F66">
         <v>308</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>2</v>
       </c>
-      <c r="G66" s="17" t="s">
+      <c r="H66" s="17" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15.75" customHeight="1">
+    <row r="67" spans="1:8" ht="15.75" customHeight="1">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -2447,14 +3441,17 @@
       <c r="D67" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E67" t="s">
-        <v>141</v>
+      <c r="E67" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F67" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G67" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" customHeight="1">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -2467,14 +3464,17 @@
       <c r="D68" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E68" t="s">
-        <v>141</v>
+      <c r="E68" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F68" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G68" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" customHeight="1">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -2487,14 +3487,17 @@
       <c r="D69" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E69" t="s">
-        <v>141</v>
+      <c r="E69" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F69" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G69" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" customHeight="1">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -2507,14 +3510,17 @@
       <c r="D70" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E70" t="s">
-        <v>141</v>
+      <c r="E70" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F70" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G70" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" customHeight="1">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -2527,32 +3533,2455 @@
       <c r="D71" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E71" t="s">
-        <v>141</v>
+      <c r="E71" s="26" t="s">
+        <v>401</v>
       </c>
       <c r="F71" t="s">
         <v>141</v>
       </c>
+      <c r="G71" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E72" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E73" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D75" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E75" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D76" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E76" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D77" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E77" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D78" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E78" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D79" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E79" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D80" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E80" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D81" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E81" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D82" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E82" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D83" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E83" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D84" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E84" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D85" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E85" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D86" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E86" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D87" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E87" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D88" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="E88" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D89" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E89" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D90" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E90" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D91" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E91" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D92" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E92" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D93" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E93" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D94" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E94" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D95" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E95" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D96" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E96" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D97" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E97" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D98" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E98" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D99" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E99" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="D100" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E100" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D101" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E101" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D102" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E102" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D103" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E103" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D104" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E104" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="D105" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E105" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D106" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E106" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="D107" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E107" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D108" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E108" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D109" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E109" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D110" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E110" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D111" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E111" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D112" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E112" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D113" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="E113" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D114" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E114" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="C115" s="11"/>
+      <c r="D115" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E115" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="C116" s="11"/>
+      <c r="D116" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E116" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D117" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E117" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D118" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E118" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D119" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E119" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D120" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E120" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D121" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E121" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D122" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E122" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D123" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E123" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D124" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E124" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D125" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E125" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D126" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E126" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D127" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E127" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D128" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E128" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D129" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E129" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="D130" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E130" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D131" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E131" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D132" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E132" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D133" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E133" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D134" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E134" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D135" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E135" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D136" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E136" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="C137" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D137" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E137" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="C138" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D138" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E138" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D139" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E139" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="C140" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D140" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E140" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="C141" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D141" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E141" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="C142" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D142" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E142" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="C143" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D143" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E143" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="C144" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D144" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E144" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C145" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D145" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E145" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D146" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E146" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="D147" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E147" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="C148" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="D148" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E148" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="C149" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="D149" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E149" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D150" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E150" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D151" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E151" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="C152" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D152" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E152" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="D153" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E153" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="C154" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D154" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E154" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="D155" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E155" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="C156" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D156" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E156" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="D157" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E157" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="C158" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="D158" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E158" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D159" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E159" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="C160" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="D160" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E160" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="C161" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D161" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E161" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="C162" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="D162" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E162" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="C163" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="D163" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E163" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="C164" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D164" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E164" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="C165" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="D165" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E165" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="C166" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D166" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E166" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="C167" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D167" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E167" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="C168" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D168" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="E168" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="C169" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="D169" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="E169" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="C170" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="D170" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="E170" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="C171" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="D171" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E171" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="C172" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="D172" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E172" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="C173" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D173" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E173" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="C174" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="D174" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E174" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="C175" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="D175" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E175" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="C176" s="11"/>
+      <c r="D176" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E176" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="C177" s="11"/>
+      <c r="D177" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E177" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="C178" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="D178" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E178" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="C179" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="D179" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E179" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="C180" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="D180" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E180" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="C181" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="D181" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E181" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="C182" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="D182" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="E182" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="C183" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D183" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E183" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="C184" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="D184" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E184" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="C185" s="11"/>
+      <c r="D185" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E185" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="C186" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D186" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E186" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="C187" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="D187" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E187" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="C188" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="D188" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E188" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="C189" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="D189" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E189" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="C190" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="D190" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E190" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191" s="24" t="s">
+        <v>359</v>
+      </c>
+      <c r="C191" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="D191" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E191" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="C192" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="D192" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E192" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="C193" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D193" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E193" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="C194" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="D194" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E194" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="C195" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D195" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E195" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="C196" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="D196" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E196" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="C197" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="D197" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E197" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="C198" s="11"/>
+      <c r="D198" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E198" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="C199" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="D199" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E199" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200" s="24" t="s">
+        <v>375</v>
+      </c>
+      <c r="C200" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="D200" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E200" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="C201" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="D201" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E201" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202" s="24" t="s">
+        <v>377</v>
+      </c>
+      <c r="C202" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="D202" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E202" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="C203" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="D203" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E203" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204" s="24" t="s">
+        <v>381</v>
+      </c>
+      <c r="C204" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="D204" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E204" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C205" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="D205" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E205" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="C206" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="D206" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E206" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207" s="24" t="s">
+        <v>387</v>
+      </c>
+      <c r="C207" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="D207" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E207" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="C208" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D208" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E208" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="C209" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D209" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E209" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="C210" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D210" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E210" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="C211" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D211" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E211" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="C212" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D212" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E212" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213" s="24" t="s">
+        <v>395</v>
+      </c>
+      <c r="C213" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="D213" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E213" s="26" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="C214" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="D214" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="E214" s="26" t="s">
+        <v>400</v>
+      </c>
+      <c r="F214" s="20"/>
+      <c r="G214" s="20"/>
+      <c r="H214" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{C64EDCD7-E648-4B6F-B381-D60669DC872C}"/>
-    <hyperlink ref="G5" r:id="rId2" xr:uid="{9D9FD61E-95EB-4393-BF28-BF13D1778A22}"/>
-    <hyperlink ref="G6" r:id="rId3" xr:uid="{F610B55B-4151-4050-B192-7872D12D34B0}"/>
-    <hyperlink ref="G7" r:id="rId4" xr:uid="{E3F9EA51-521B-4DAE-9713-6AD9F445AC7F}"/>
-    <hyperlink ref="G10" r:id="rId5" xr:uid="{7FF656D8-A61F-4667-A401-2E6206385EE0}"/>
-    <hyperlink ref="G26" r:id="rId6" xr:uid="{E8A4E134-0086-49B6-8472-7876F8F64F1C}"/>
-    <hyperlink ref="G43" r:id="rId7" xr:uid="{976E7F0C-70B2-4432-BE3C-0970D7A90082}"/>
-    <hyperlink ref="G46" r:id="rId8" xr:uid="{32D2DE3C-B3D5-43E9-8AD6-DE377A726E00}"/>
-    <hyperlink ref="G47" r:id="rId9" xr:uid="{3373E799-271C-478C-93A3-20DCE391E153}"/>
-    <hyperlink ref="G50" r:id="rId10" xr:uid="{19871289-CC85-4E70-A5CD-449DF7D602DB}"/>
-    <hyperlink ref="G52" r:id="rId11" xr:uid="{17026F9F-5CDC-4C2E-BB44-401D5EDDB6D1}"/>
-    <hyperlink ref="G53" r:id="rId12" xr:uid="{22AEE8E8-D77B-4E6D-83FB-6698E8F3A83B}"/>
-    <hyperlink ref="G62" r:id="rId13" xr:uid="{A23433BD-83ED-46DA-917F-C9309F775085}"/>
-    <hyperlink ref="G63" r:id="rId14" xr:uid="{E0EF9F06-B69A-4D57-9FD3-325C74FE1D55}"/>
-    <hyperlink ref="G64" r:id="rId15" xr:uid="{2A2BCD34-09E8-4DE2-9FE9-AB86792AF89B}"/>
-    <hyperlink ref="G65" r:id="rId16" xr:uid="{85C19C63-2D5A-414B-B0AC-999D82D87E4A}"/>
-    <hyperlink ref="G66" r:id="rId17" xr:uid="{F607233C-7AAC-407C-B20E-040315068988}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{C64EDCD7-E648-4B6F-B381-D60669DC872C}"/>
+    <hyperlink ref="H5" r:id="rId2" xr:uid="{9D9FD61E-95EB-4393-BF28-BF13D1778A22}"/>
+    <hyperlink ref="H6" r:id="rId3" xr:uid="{F610B55B-4151-4050-B192-7872D12D34B0}"/>
+    <hyperlink ref="H7" r:id="rId4" xr:uid="{E3F9EA51-521B-4DAE-9713-6AD9F445AC7F}"/>
+    <hyperlink ref="H10" r:id="rId5" xr:uid="{7FF656D8-A61F-4667-A401-2E6206385EE0}"/>
+    <hyperlink ref="H26" r:id="rId6" xr:uid="{E8A4E134-0086-49B6-8472-7876F8F64F1C}"/>
+    <hyperlink ref="H43" r:id="rId7" xr:uid="{976E7F0C-70B2-4432-BE3C-0970D7A90082}"/>
+    <hyperlink ref="H46" r:id="rId8" xr:uid="{32D2DE3C-B3D5-43E9-8AD6-DE377A726E00}"/>
+    <hyperlink ref="H47" r:id="rId9" xr:uid="{3373E799-271C-478C-93A3-20DCE391E153}"/>
+    <hyperlink ref="H50" r:id="rId10" xr:uid="{19871289-CC85-4E70-A5CD-449DF7D602DB}"/>
+    <hyperlink ref="H52" r:id="rId11" xr:uid="{17026F9F-5CDC-4C2E-BB44-401D5EDDB6D1}"/>
+    <hyperlink ref="H53" r:id="rId12" xr:uid="{22AEE8E8-D77B-4E6D-83FB-6698E8F3A83B}"/>
+    <hyperlink ref="H62" r:id="rId13" xr:uid="{A23433BD-83ED-46DA-917F-C9309F775085}"/>
+    <hyperlink ref="H63" r:id="rId14" xr:uid="{E0EF9F06-B69A-4D57-9FD3-325C74FE1D55}"/>
+    <hyperlink ref="H64" r:id="rId15" xr:uid="{2A2BCD34-09E8-4DE2-9FE9-AB86792AF89B}"/>
+    <hyperlink ref="H65" r:id="rId16" xr:uid="{85C19C63-2D5A-414B-B0AC-999D82D87E4A}"/>
+    <hyperlink ref="H66" r:id="rId17" xr:uid="{F607233C-7AAC-407C-B20E-040315068988}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
